--- a/VerveStacks_POL_grids_kan10/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan10/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49135443-84A5-4CA9-A7A1-B80228245CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3100CBF8-2197-4D79-8B06-DFB13CCE6718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AB02C001-04E4-4AC2-9E3A-1341B33CF027}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{AB02C001-04E4-4AC2-9E3A-1341B33CF027}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7408" uniqueCount="1134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7231" uniqueCount="1135">
   <si>
     <t>~fi_t</t>
   </si>
@@ -3444,6 +3444,9 @@
   </si>
   <si>
     <t>ccs retrofit of -- Blachownia Manufacturing Plant power station_TG4 -- operating -- CHP (captive)</t>
+  </si>
+  <si>
+    <t>\I: POL</t>
   </si>
 </sst>
 </file>
@@ -3892,8 +3895,9 @@
       <c r="B11" t="s">
         <v>780</v>
       </c>
-      <c r="C11" t="s">
-        <v>15</v>
+      <c r="C11" t="str">
+        <f>Q11</f>
+        <v>\I: POL</v>
       </c>
       <c r="D11" t="s">
         <v>50</v>
@@ -3932,7 +3936,7 @@
         <v>780</v>
       </c>
       <c r="Q11" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R11" t="s">
         <v>957</v>
@@ -3954,8 +3958,9 @@
       <c r="B12" t="s">
         <v>781</v>
       </c>
-      <c r="C12" t="s">
-        <v>15</v>
+      <c r="C12" t="str">
+        <f t="shared" ref="C12:C75" si="0">Q12</f>
+        <v>\I: POL</v>
       </c>
       <c r="D12" t="s">
         <v>50</v>
@@ -3994,7 +3999,7 @@
         <v>781</v>
       </c>
       <c r="Q12" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R12" t="s">
         <v>958</v>
@@ -4016,8 +4021,9 @@
       <c r="B13" t="s">
         <v>782</v>
       </c>
-      <c r="C13" t="s">
-        <v>15</v>
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D13" t="s">
         <v>50</v>
@@ -4056,7 +4062,7 @@
         <v>782</v>
       </c>
       <c r="Q13" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R13" t="s">
         <v>959</v>
@@ -4078,8 +4084,9 @@
       <c r="B14" t="s">
         <v>783</v>
       </c>
-      <c r="C14" t="s">
-        <v>15</v>
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D14" t="s">
         <v>50</v>
@@ -4118,7 +4125,7 @@
         <v>783</v>
       </c>
       <c r="Q14" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R14" t="s">
         <v>960</v>
@@ -4140,8 +4147,9 @@
       <c r="B15" t="s">
         <v>784</v>
       </c>
-      <c r="C15" t="s">
-        <v>15</v>
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D15" t="s">
         <v>50</v>
@@ -4180,7 +4188,7 @@
         <v>784</v>
       </c>
       <c r="Q15" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R15" t="s">
         <v>961</v>
@@ -4202,8 +4210,9 @@
       <c r="B16" t="s">
         <v>785</v>
       </c>
-      <c r="C16" t="s">
-        <v>15</v>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D16" t="s">
         <v>50</v>
@@ -4242,7 +4251,7 @@
         <v>785</v>
       </c>
       <c r="Q16" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R16" t="s">
         <v>962</v>
@@ -4264,8 +4273,9 @@
       <c r="B17" t="s">
         <v>786</v>
       </c>
-      <c r="C17" t="s">
-        <v>15</v>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D17" t="s">
         <v>50</v>
@@ -4304,7 +4314,7 @@
         <v>786</v>
       </c>
       <c r="Q17" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R17" t="s">
         <v>963</v>
@@ -4326,8 +4336,9 @@
       <c r="B18" t="s">
         <v>787</v>
       </c>
-      <c r="C18" t="s">
-        <v>15</v>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D18" t="s">
         <v>50</v>
@@ -4366,7 +4377,7 @@
         <v>787</v>
       </c>
       <c r="Q18" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R18" t="s">
         <v>964</v>
@@ -4388,8 +4399,9 @@
       <c r="B19" t="s">
         <v>788</v>
       </c>
-      <c r="C19" t="s">
-        <v>15</v>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D19" t="s">
         <v>50</v>
@@ -4428,7 +4440,7 @@
         <v>788</v>
       </c>
       <c r="Q19" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R19" t="s">
         <v>965</v>
@@ -4450,8 +4462,9 @@
       <c r="B20" t="s">
         <v>789</v>
       </c>
-      <c r="C20" t="s">
-        <v>15</v>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D20" t="s">
         <v>50</v>
@@ -4490,7 +4503,7 @@
         <v>789</v>
       </c>
       <c r="Q20" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R20" t="s">
         <v>966</v>
@@ -4512,8 +4525,9 @@
       <c r="B21" t="s">
         <v>790</v>
       </c>
-      <c r="C21" t="s">
-        <v>15</v>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D21" t="s">
         <v>50</v>
@@ -4552,7 +4566,7 @@
         <v>790</v>
       </c>
       <c r="Q21" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R21" t="s">
         <v>967</v>
@@ -4574,8 +4588,9 @@
       <c r="B22" t="s">
         <v>791</v>
       </c>
-      <c r="C22" t="s">
-        <v>15</v>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D22" t="s">
         <v>50</v>
@@ -4614,7 +4629,7 @@
         <v>791</v>
       </c>
       <c r="Q22" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R22" t="s">
         <v>968</v>
@@ -4636,8 +4651,9 @@
       <c r="B23" t="s">
         <v>792</v>
       </c>
-      <c r="C23" t="s">
-        <v>15</v>
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D23" t="s">
         <v>50</v>
@@ -4676,7 +4692,7 @@
         <v>792</v>
       </c>
       <c r="Q23" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R23" t="s">
         <v>969</v>
@@ -4698,8 +4714,9 @@
       <c r="B24" t="s">
         <v>793</v>
       </c>
-      <c r="C24" t="s">
-        <v>15</v>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D24" t="s">
         <v>50</v>
@@ -4738,7 +4755,7 @@
         <v>793</v>
       </c>
       <c r="Q24" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R24" t="s">
         <v>970</v>
@@ -4760,8 +4777,9 @@
       <c r="B25" t="s">
         <v>794</v>
       </c>
-      <c r="C25" t="s">
-        <v>15</v>
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D25" t="s">
         <v>50</v>
@@ -4800,7 +4818,7 @@
         <v>794</v>
       </c>
       <c r="Q25" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R25" t="s">
         <v>971</v>
@@ -4822,8 +4840,9 @@
       <c r="B26" t="s">
         <v>795</v>
       </c>
-      <c r="C26" t="s">
-        <v>15</v>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D26" t="s">
         <v>50</v>
@@ -4862,7 +4881,7 @@
         <v>795</v>
       </c>
       <c r="Q26" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R26" t="s">
         <v>972</v>
@@ -4884,8 +4903,9 @@
       <c r="B27" t="s">
         <v>796</v>
       </c>
-      <c r="C27" t="s">
-        <v>15</v>
+      <c r="C27" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D27" t="s">
         <v>50</v>
@@ -4924,7 +4944,7 @@
         <v>796</v>
       </c>
       <c r="Q27" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R27" t="s">
         <v>973</v>
@@ -4946,8 +4966,9 @@
       <c r="B28" t="s">
         <v>797</v>
       </c>
-      <c r="C28" t="s">
-        <v>15</v>
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D28" t="s">
         <v>50</v>
@@ -4986,7 +5007,7 @@
         <v>797</v>
       </c>
       <c r="Q28" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R28" t="s">
         <v>974</v>
@@ -5008,8 +5029,9 @@
       <c r="B29" t="s">
         <v>798</v>
       </c>
-      <c r="C29" t="s">
-        <v>15</v>
+      <c r="C29" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D29" t="s">
         <v>50</v>
@@ -5048,7 +5070,7 @@
         <v>798</v>
       </c>
       <c r="Q29" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R29" t="s">
         <v>975</v>
@@ -5070,8 +5092,9 @@
       <c r="B30" t="s">
         <v>799</v>
       </c>
-      <c r="C30" t="s">
-        <v>15</v>
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D30" t="s">
         <v>50</v>
@@ -5110,7 +5133,7 @@
         <v>799</v>
       </c>
       <c r="Q30" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R30" t="s">
         <v>976</v>
@@ -5132,8 +5155,9 @@
       <c r="B31" t="s">
         <v>800</v>
       </c>
-      <c r="C31" t="s">
-        <v>15</v>
+      <c r="C31" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D31" t="s">
         <v>50</v>
@@ -5172,7 +5196,7 @@
         <v>800</v>
       </c>
       <c r="Q31" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R31" t="s">
         <v>977</v>
@@ -5194,8 +5218,9 @@
       <c r="B32" t="s">
         <v>801</v>
       </c>
-      <c r="C32" t="s">
-        <v>15</v>
+      <c r="C32" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D32" t="s">
         <v>50</v>
@@ -5234,7 +5259,7 @@
         <v>801</v>
       </c>
       <c r="Q32" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R32" t="s">
         <v>978</v>
@@ -5256,8 +5281,9 @@
       <c r="B33" t="s">
         <v>802</v>
       </c>
-      <c r="C33" t="s">
-        <v>15</v>
+      <c r="C33" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D33" t="s">
         <v>50</v>
@@ -5296,7 +5322,7 @@
         <v>802</v>
       </c>
       <c r="Q33" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R33" t="s">
         <v>979</v>
@@ -5318,8 +5344,9 @@
       <c r="B34" t="s">
         <v>803</v>
       </c>
-      <c r="C34" t="s">
-        <v>15</v>
+      <c r="C34" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D34" t="s">
         <v>50</v>
@@ -5358,7 +5385,7 @@
         <v>803</v>
       </c>
       <c r="Q34" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R34" t="s">
         <v>980</v>
@@ -5380,8 +5407,9 @@
       <c r="B35" t="s">
         <v>804</v>
       </c>
-      <c r="C35" t="s">
-        <v>15</v>
+      <c r="C35" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D35" t="s">
         <v>50</v>
@@ -5420,7 +5448,7 @@
         <v>804</v>
       </c>
       <c r="Q35" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R35" t="s">
         <v>981</v>
@@ -5442,8 +5470,9 @@
       <c r="B36" t="s">
         <v>805</v>
       </c>
-      <c r="C36" t="s">
-        <v>15</v>
+      <c r="C36" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D36" t="s">
         <v>50</v>
@@ -5482,7 +5511,7 @@
         <v>805</v>
       </c>
       <c r="Q36" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R36" t="s">
         <v>982</v>
@@ -5504,8 +5533,9 @@
       <c r="B37" t="s">
         <v>806</v>
       </c>
-      <c r="C37" t="s">
-        <v>15</v>
+      <c r="C37" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D37" t="s">
         <v>50</v>
@@ -5544,7 +5574,7 @@
         <v>806</v>
       </c>
       <c r="Q37" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R37" t="s">
         <v>983</v>
@@ -5566,8 +5596,9 @@
       <c r="B38" t="s">
         <v>807</v>
       </c>
-      <c r="C38" t="s">
-        <v>15</v>
+      <c r="C38" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D38" t="s">
         <v>50</v>
@@ -5606,7 +5637,7 @@
         <v>807</v>
       </c>
       <c r="Q38" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R38" t="s">
         <v>984</v>
@@ -5628,8 +5659,9 @@
       <c r="B39" t="s">
         <v>808</v>
       </c>
-      <c r="C39" t="s">
-        <v>15</v>
+      <c r="C39" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D39" t="s">
         <v>50</v>
@@ -5668,7 +5700,7 @@
         <v>808</v>
       </c>
       <c r="Q39" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R39" t="s">
         <v>985</v>
@@ -5690,8 +5722,9 @@
       <c r="B40" t="s">
         <v>809</v>
       </c>
-      <c r="C40" t="s">
-        <v>15</v>
+      <c r="C40" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D40" t="s">
         <v>50</v>
@@ -5730,7 +5763,7 @@
         <v>809</v>
       </c>
       <c r="Q40" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R40" t="s">
         <v>986</v>
@@ -5752,8 +5785,9 @@
       <c r="B41" t="s">
         <v>810</v>
       </c>
-      <c r="C41" t="s">
-        <v>15</v>
+      <c r="C41" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D41" t="s">
         <v>50</v>
@@ -5792,7 +5826,7 @@
         <v>810</v>
       </c>
       <c r="Q41" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R41" t="s">
         <v>987</v>
@@ -5814,8 +5848,9 @@
       <c r="B42" t="s">
         <v>811</v>
       </c>
-      <c r="C42" t="s">
-        <v>15</v>
+      <c r="C42" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D42" t="s">
         <v>50</v>
@@ -5854,7 +5889,7 @@
         <v>811</v>
       </c>
       <c r="Q42" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R42" t="s">
         <v>988</v>
@@ -5876,8 +5911,9 @@
       <c r="B43" t="s">
         <v>812</v>
       </c>
-      <c r="C43" t="s">
-        <v>15</v>
+      <c r="C43" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D43" t="s">
         <v>50</v>
@@ -5916,7 +5952,7 @@
         <v>812</v>
       </c>
       <c r="Q43" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R43" t="s">
         <v>989</v>
@@ -5938,8 +5974,9 @@
       <c r="B44" t="s">
         <v>813</v>
       </c>
-      <c r="C44" t="s">
-        <v>15</v>
+      <c r="C44" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D44" t="s">
         <v>50</v>
@@ -5978,7 +6015,7 @@
         <v>813</v>
       </c>
       <c r="Q44" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R44" t="s">
         <v>990</v>
@@ -6000,8 +6037,9 @@
       <c r="B45" t="s">
         <v>814</v>
       </c>
-      <c r="C45" t="s">
-        <v>15</v>
+      <c r="C45" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D45" t="s">
         <v>50</v>
@@ -6040,7 +6078,7 @@
         <v>814</v>
       </c>
       <c r="Q45" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R45" t="s">
         <v>991</v>
@@ -6062,8 +6100,9 @@
       <c r="B46" t="s">
         <v>815</v>
       </c>
-      <c r="C46" t="s">
-        <v>15</v>
+      <c r="C46" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D46" t="s">
         <v>50</v>
@@ -6102,7 +6141,7 @@
         <v>815</v>
       </c>
       <c r="Q46" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R46" t="s">
         <v>992</v>
@@ -6124,8 +6163,9 @@
       <c r="B47" t="s">
         <v>816</v>
       </c>
-      <c r="C47" t="s">
-        <v>15</v>
+      <c r="C47" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D47" t="s">
         <v>50</v>
@@ -6164,7 +6204,7 @@
         <v>816</v>
       </c>
       <c r="Q47" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R47" t="s">
         <v>993</v>
@@ -6186,8 +6226,9 @@
       <c r="B48" t="s">
         <v>817</v>
       </c>
-      <c r="C48" t="s">
-        <v>15</v>
+      <c r="C48" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D48" t="s">
         <v>50</v>
@@ -6226,7 +6267,7 @@
         <v>817</v>
       </c>
       <c r="Q48" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R48" t="s">
         <v>994</v>
@@ -6248,8 +6289,9 @@
       <c r="B49" t="s">
         <v>818</v>
       </c>
-      <c r="C49" t="s">
-        <v>15</v>
+      <c r="C49" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D49" t="s">
         <v>50</v>
@@ -6288,7 +6330,7 @@
         <v>818</v>
       </c>
       <c r="Q49" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R49" t="s">
         <v>995</v>
@@ -6310,8 +6352,9 @@
       <c r="B50" t="s">
         <v>819</v>
       </c>
-      <c r="C50" t="s">
-        <v>15</v>
+      <c r="C50" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D50" t="s">
         <v>50</v>
@@ -6350,7 +6393,7 @@
         <v>819</v>
       </c>
       <c r="Q50" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R50" t="s">
         <v>996</v>
@@ -6372,8 +6415,9 @@
       <c r="B51" t="s">
         <v>820</v>
       </c>
-      <c r="C51" t="s">
-        <v>15</v>
+      <c r="C51" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D51" t="s">
         <v>50</v>
@@ -6412,7 +6456,7 @@
         <v>820</v>
       </c>
       <c r="Q51" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R51" t="s">
         <v>997</v>
@@ -6434,8 +6478,9 @@
       <c r="B52" t="s">
         <v>821</v>
       </c>
-      <c r="C52" t="s">
-        <v>15</v>
+      <c r="C52" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D52" t="s">
         <v>50</v>
@@ -6474,7 +6519,7 @@
         <v>821</v>
       </c>
       <c r="Q52" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R52" t="s">
         <v>998</v>
@@ -6496,8 +6541,9 @@
       <c r="B53" t="s">
         <v>822</v>
       </c>
-      <c r="C53" t="s">
-        <v>15</v>
+      <c r="C53" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D53" t="s">
         <v>50</v>
@@ -6536,7 +6582,7 @@
         <v>822</v>
       </c>
       <c r="Q53" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R53" t="s">
         <v>999</v>
@@ -6558,8 +6604,9 @@
       <c r="B54" t="s">
         <v>823</v>
       </c>
-      <c r="C54" t="s">
-        <v>15</v>
+      <c r="C54" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D54" t="s">
         <v>50</v>
@@ -6598,7 +6645,7 @@
         <v>823</v>
       </c>
       <c r="Q54" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R54" t="s">
         <v>1000</v>
@@ -6620,8 +6667,9 @@
       <c r="B55" t="s">
         <v>824</v>
       </c>
-      <c r="C55" t="s">
-        <v>15</v>
+      <c r="C55" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D55" t="s">
         <v>50</v>
@@ -6660,7 +6708,7 @@
         <v>824</v>
       </c>
       <c r="Q55" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R55" t="s">
         <v>1001</v>
@@ -6682,8 +6730,9 @@
       <c r="B56" t="s">
         <v>825</v>
       </c>
-      <c r="C56" t="s">
-        <v>15</v>
+      <c r="C56" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D56" t="s">
         <v>50</v>
@@ -6722,7 +6771,7 @@
         <v>825</v>
       </c>
       <c r="Q56" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R56" t="s">
         <v>1002</v>
@@ -6744,8 +6793,9 @@
       <c r="B57" t="s">
         <v>826</v>
       </c>
-      <c r="C57" t="s">
-        <v>15</v>
+      <c r="C57" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D57" t="s">
         <v>50</v>
@@ -6784,7 +6834,7 @@
         <v>826</v>
       </c>
       <c r="Q57" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R57" t="s">
         <v>1003</v>
@@ -6806,8 +6856,9 @@
       <c r="B58" t="s">
         <v>827</v>
       </c>
-      <c r="C58" t="s">
-        <v>15</v>
+      <c r="C58" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D58" t="s">
         <v>50</v>
@@ -6846,7 +6897,7 @@
         <v>827</v>
       </c>
       <c r="Q58" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R58" t="s">
         <v>1004</v>
@@ -6868,8 +6919,9 @@
       <c r="B59" t="s">
         <v>828</v>
       </c>
-      <c r="C59" t="s">
-        <v>15</v>
+      <c r="C59" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D59" t="s">
         <v>50</v>
@@ -6908,7 +6960,7 @@
         <v>828</v>
       </c>
       <c r="Q59" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R59" t="s">
         <v>1005</v>
@@ -6930,8 +6982,9 @@
       <c r="B60" t="s">
         <v>829</v>
       </c>
-      <c r="C60" t="s">
-        <v>15</v>
+      <c r="C60" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D60" t="s">
         <v>50</v>
@@ -6970,7 +7023,7 @@
         <v>829</v>
       </c>
       <c r="Q60" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R60" t="s">
         <v>1006</v>
@@ -6992,8 +7045,9 @@
       <c r="B61" t="s">
         <v>830</v>
       </c>
-      <c r="C61" t="s">
-        <v>15</v>
+      <c r="C61" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D61" t="s">
         <v>50</v>
@@ -7032,7 +7086,7 @@
         <v>830</v>
       </c>
       <c r="Q61" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R61" t="s">
         <v>1007</v>
@@ -7054,8 +7108,9 @@
       <c r="B62" t="s">
         <v>831</v>
       </c>
-      <c r="C62" t="s">
-        <v>15</v>
+      <c r="C62" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D62" t="s">
         <v>50</v>
@@ -7094,7 +7149,7 @@
         <v>831</v>
       </c>
       <c r="Q62" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R62" t="s">
         <v>1008</v>
@@ -7116,8 +7171,9 @@
       <c r="B63" t="s">
         <v>832</v>
       </c>
-      <c r="C63" t="s">
-        <v>15</v>
+      <c r="C63" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D63" t="s">
         <v>50</v>
@@ -7156,7 +7212,7 @@
         <v>832</v>
       </c>
       <c r="Q63" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R63" t="s">
         <v>1009</v>
@@ -7178,8 +7234,9 @@
       <c r="B64" t="s">
         <v>833</v>
       </c>
-      <c r="C64" t="s">
-        <v>15</v>
+      <c r="C64" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D64" t="s">
         <v>50</v>
@@ -7218,7 +7275,7 @@
         <v>833</v>
       </c>
       <c r="Q64" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R64" t="s">
         <v>1010</v>
@@ -7240,8 +7297,9 @@
       <c r="B65" t="s">
         <v>834</v>
       </c>
-      <c r="C65" t="s">
-        <v>15</v>
+      <c r="C65" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D65" t="s">
         <v>50</v>
@@ -7280,7 +7338,7 @@
         <v>834</v>
       </c>
       <c r="Q65" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R65" t="s">
         <v>1011</v>
@@ -7302,8 +7360,9 @@
       <c r="B66" t="s">
         <v>835</v>
       </c>
-      <c r="C66" t="s">
-        <v>15</v>
+      <c r="C66" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D66" t="s">
         <v>50</v>
@@ -7342,7 +7401,7 @@
         <v>835</v>
       </c>
       <c r="Q66" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R66" t="s">
         <v>1012</v>
@@ -7364,8 +7423,9 @@
       <c r="B67" t="s">
         <v>836</v>
       </c>
-      <c r="C67" t="s">
-        <v>15</v>
+      <c r="C67" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D67" t="s">
         <v>50</v>
@@ -7404,7 +7464,7 @@
         <v>836</v>
       </c>
       <c r="Q67" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R67" t="s">
         <v>1013</v>
@@ -7426,8 +7486,9 @@
       <c r="B68" t="s">
         <v>837</v>
       </c>
-      <c r="C68" t="s">
-        <v>15</v>
+      <c r="C68" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D68" t="s">
         <v>50</v>
@@ -7466,7 +7527,7 @@
         <v>837</v>
       </c>
       <c r="Q68" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R68" t="s">
         <v>1014</v>
@@ -7488,8 +7549,9 @@
       <c r="B69" t="s">
         <v>838</v>
       </c>
-      <c r="C69" t="s">
-        <v>15</v>
+      <c r="C69" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D69" t="s">
         <v>50</v>
@@ -7528,7 +7590,7 @@
         <v>838</v>
       </c>
       <c r="Q69" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R69" t="s">
         <v>1015</v>
@@ -7550,8 +7612,9 @@
       <c r="B70" t="s">
         <v>839</v>
       </c>
-      <c r="C70" t="s">
-        <v>15</v>
+      <c r="C70" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D70" t="s">
         <v>50</v>
@@ -7590,7 +7653,7 @@
         <v>839</v>
       </c>
       <c r="Q70" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R70" t="s">
         <v>1016</v>
@@ -7612,8 +7675,9 @@
       <c r="B71" t="s">
         <v>840</v>
       </c>
-      <c r="C71" t="s">
-        <v>15</v>
+      <c r="C71" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D71" t="s">
         <v>50</v>
@@ -7652,7 +7716,7 @@
         <v>840</v>
       </c>
       <c r="Q71" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R71" t="s">
         <v>1017</v>
@@ -7674,8 +7738,9 @@
       <c r="B72" t="s">
         <v>841</v>
       </c>
-      <c r="C72" t="s">
-        <v>15</v>
+      <c r="C72" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D72" t="s">
         <v>50</v>
@@ -7714,7 +7779,7 @@
         <v>841</v>
       </c>
       <c r="Q72" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R72" t="s">
         <v>1018</v>
@@ -7736,8 +7801,9 @@
       <c r="B73" t="s">
         <v>842</v>
       </c>
-      <c r="C73" t="s">
-        <v>15</v>
+      <c r="C73" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D73" t="s">
         <v>50</v>
@@ -7776,7 +7842,7 @@
         <v>842</v>
       </c>
       <c r="Q73" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R73" t="s">
         <v>1019</v>
@@ -7798,8 +7864,9 @@
       <c r="B74" t="s">
         <v>843</v>
       </c>
-      <c r="C74" t="s">
-        <v>15</v>
+      <c r="C74" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D74" t="s">
         <v>50</v>
@@ -7838,7 +7905,7 @@
         <v>843</v>
       </c>
       <c r="Q74" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R74" t="s">
         <v>1020</v>
@@ -7860,8 +7927,9 @@
       <c r="B75" t="s">
         <v>844</v>
       </c>
-      <c r="C75" t="s">
-        <v>15</v>
+      <c r="C75" t="str">
+        <f t="shared" si="0"/>
+        <v>\I: POL</v>
       </c>
       <c r="D75" t="s">
         <v>50</v>
@@ -7900,7 +7968,7 @@
         <v>844</v>
       </c>
       <c r="Q75" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R75" t="s">
         <v>1021</v>
@@ -7922,8 +7990,9 @@
       <c r="B76" t="s">
         <v>845</v>
       </c>
-      <c r="C76" t="s">
-        <v>15</v>
+      <c r="C76" t="str">
+        <f t="shared" ref="C76:C139" si="1">Q76</f>
+        <v>\I: POL</v>
       </c>
       <c r="D76" t="s">
         <v>50</v>
@@ -7962,7 +8031,7 @@
         <v>845</v>
       </c>
       <c r="Q76" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R76" t="s">
         <v>1022</v>
@@ -7984,8 +8053,9 @@
       <c r="B77" t="s">
         <v>846</v>
       </c>
-      <c r="C77" t="s">
-        <v>15</v>
+      <c r="C77" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D77" t="s">
         <v>50</v>
@@ -8024,7 +8094,7 @@
         <v>846</v>
       </c>
       <c r="Q77" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R77" t="s">
         <v>1023</v>
@@ -8046,8 +8116,9 @@
       <c r="B78" t="s">
         <v>847</v>
       </c>
-      <c r="C78" t="s">
-        <v>15</v>
+      <c r="C78" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D78" t="s">
         <v>50</v>
@@ -8086,7 +8157,7 @@
         <v>847</v>
       </c>
       <c r="Q78" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R78" t="s">
         <v>1024</v>
@@ -8108,8 +8179,9 @@
       <c r="B79" t="s">
         <v>848</v>
       </c>
-      <c r="C79" t="s">
-        <v>15</v>
+      <c r="C79" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D79" t="s">
         <v>50</v>
@@ -8148,7 +8220,7 @@
         <v>848</v>
       </c>
       <c r="Q79" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R79" t="s">
         <v>1025</v>
@@ -8170,8 +8242,9 @@
       <c r="B80" t="s">
         <v>849</v>
       </c>
-      <c r="C80" t="s">
-        <v>15</v>
+      <c r="C80" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D80" t="s">
         <v>50</v>
@@ -8210,7 +8283,7 @@
         <v>849</v>
       </c>
       <c r="Q80" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R80" t="s">
         <v>1026</v>
@@ -8232,8 +8305,9 @@
       <c r="B81" t="s">
         <v>850</v>
       </c>
-      <c r="C81" t="s">
-        <v>15</v>
+      <c r="C81" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D81" t="s">
         <v>50</v>
@@ -8272,7 +8346,7 @@
         <v>850</v>
       </c>
       <c r="Q81" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R81" t="s">
         <v>1027</v>
@@ -8294,8 +8368,9 @@
       <c r="B82" t="s">
         <v>851</v>
       </c>
-      <c r="C82" t="s">
-        <v>15</v>
+      <c r="C82" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D82" t="s">
         <v>50</v>
@@ -8334,7 +8409,7 @@
         <v>851</v>
       </c>
       <c r="Q82" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R82" t="s">
         <v>1028</v>
@@ -8356,8 +8431,9 @@
       <c r="B83" t="s">
         <v>852</v>
       </c>
-      <c r="C83" t="s">
-        <v>15</v>
+      <c r="C83" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D83" t="s">
         <v>50</v>
@@ -8396,7 +8472,7 @@
         <v>852</v>
       </c>
       <c r="Q83" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R83" t="s">
         <v>1029</v>
@@ -8418,8 +8494,9 @@
       <c r="B84" t="s">
         <v>853</v>
       </c>
-      <c r="C84" t="s">
-        <v>15</v>
+      <c r="C84" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D84" t="s">
         <v>50</v>
@@ -8458,7 +8535,7 @@
         <v>853</v>
       </c>
       <c r="Q84" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R84" t="s">
         <v>1030</v>
@@ -8480,8 +8557,9 @@
       <c r="B85" t="s">
         <v>854</v>
       </c>
-      <c r="C85" t="s">
-        <v>15</v>
+      <c r="C85" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D85" t="s">
         <v>50</v>
@@ -8520,7 +8598,7 @@
         <v>854</v>
       </c>
       <c r="Q85" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R85" t="s">
         <v>1031</v>
@@ -8542,8 +8620,9 @@
       <c r="B86" t="s">
         <v>855</v>
       </c>
-      <c r="C86" t="s">
-        <v>15</v>
+      <c r="C86" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D86" t="s">
         <v>50</v>
@@ -8582,7 +8661,7 @@
         <v>855</v>
       </c>
       <c r="Q86" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R86" t="s">
         <v>1032</v>
@@ -8604,8 +8683,9 @@
       <c r="B87" t="s">
         <v>856</v>
       </c>
-      <c r="C87" t="s">
-        <v>15</v>
+      <c r="C87" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D87" t="s">
         <v>50</v>
@@ -8644,7 +8724,7 @@
         <v>856</v>
       </c>
       <c r="Q87" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R87" t="s">
         <v>1033</v>
@@ -8666,8 +8746,9 @@
       <c r="B88" t="s">
         <v>857</v>
       </c>
-      <c r="C88" t="s">
-        <v>15</v>
+      <c r="C88" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D88" t="s">
         <v>50</v>
@@ -8706,7 +8787,7 @@
         <v>857</v>
       </c>
       <c r="Q88" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R88" t="s">
         <v>1034</v>
@@ -8728,8 +8809,9 @@
       <c r="B89" t="s">
         <v>858</v>
       </c>
-      <c r="C89" t="s">
-        <v>15</v>
+      <c r="C89" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D89" t="s">
         <v>50</v>
@@ -8768,7 +8850,7 @@
         <v>858</v>
       </c>
       <c r="Q89" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R89" t="s">
         <v>1035</v>
@@ -8790,8 +8872,9 @@
       <c r="B90" t="s">
         <v>859</v>
       </c>
-      <c r="C90" t="s">
-        <v>15</v>
+      <c r="C90" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D90" t="s">
         <v>50</v>
@@ -8830,7 +8913,7 @@
         <v>859</v>
       </c>
       <c r="Q90" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R90" t="s">
         <v>1036</v>
@@ -8852,8 +8935,9 @@
       <c r="B91" t="s">
         <v>860</v>
       </c>
-      <c r="C91" t="s">
-        <v>15</v>
+      <c r="C91" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D91" t="s">
         <v>50</v>
@@ -8892,7 +8976,7 @@
         <v>860</v>
       </c>
       <c r="Q91" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R91" t="s">
         <v>1037</v>
@@ -8914,8 +8998,9 @@
       <c r="B92" t="s">
         <v>861</v>
       </c>
-      <c r="C92" t="s">
-        <v>15</v>
+      <c r="C92" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D92" t="s">
         <v>50</v>
@@ -8954,7 +9039,7 @@
         <v>861</v>
       </c>
       <c r="Q92" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R92" t="s">
         <v>1038</v>
@@ -8976,8 +9061,9 @@
       <c r="B93" t="s">
         <v>862</v>
       </c>
-      <c r="C93" t="s">
-        <v>15</v>
+      <c r="C93" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D93" t="s">
         <v>50</v>
@@ -9016,7 +9102,7 @@
         <v>862</v>
       </c>
       <c r="Q93" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R93" t="s">
         <v>1039</v>
@@ -9038,8 +9124,9 @@
       <c r="B94" t="s">
         <v>863</v>
       </c>
-      <c r="C94" t="s">
-        <v>15</v>
+      <c r="C94" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D94" t="s">
         <v>50</v>
@@ -9078,7 +9165,7 @@
         <v>863</v>
       </c>
       <c r="Q94" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R94" t="s">
         <v>1040</v>
@@ -9100,8 +9187,9 @@
       <c r="B95" t="s">
         <v>864</v>
       </c>
-      <c r="C95" t="s">
-        <v>15</v>
+      <c r="C95" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D95" t="s">
         <v>50</v>
@@ -9140,7 +9228,7 @@
         <v>864</v>
       </c>
       <c r="Q95" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R95" t="s">
         <v>1041</v>
@@ -9162,8 +9250,9 @@
       <c r="B96" t="s">
         <v>865</v>
       </c>
-      <c r="C96" t="s">
-        <v>15</v>
+      <c r="C96" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D96" t="s">
         <v>50</v>
@@ -9202,7 +9291,7 @@
         <v>865</v>
       </c>
       <c r="Q96" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R96" t="s">
         <v>1042</v>
@@ -9224,8 +9313,9 @@
       <c r="B97" t="s">
         <v>866</v>
       </c>
-      <c r="C97" t="s">
-        <v>15</v>
+      <c r="C97" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D97" t="s">
         <v>50</v>
@@ -9264,7 +9354,7 @@
         <v>866</v>
       </c>
       <c r="Q97" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R97" t="s">
         <v>1043</v>
@@ -9286,8 +9376,9 @@
       <c r="B98" t="s">
         <v>867</v>
       </c>
-      <c r="C98" t="s">
-        <v>15</v>
+      <c r="C98" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D98" t="s">
         <v>50</v>
@@ -9326,7 +9417,7 @@
         <v>867</v>
       </c>
       <c r="Q98" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R98" t="s">
         <v>1044</v>
@@ -9348,8 +9439,9 @@
       <c r="B99" t="s">
         <v>868</v>
       </c>
-      <c r="C99" t="s">
-        <v>15</v>
+      <c r="C99" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D99" t="s">
         <v>50</v>
@@ -9388,7 +9480,7 @@
         <v>868</v>
       </c>
       <c r="Q99" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R99" t="s">
         <v>1045</v>
@@ -9410,8 +9502,9 @@
       <c r="B100" t="s">
         <v>869</v>
       </c>
-      <c r="C100" t="s">
-        <v>15</v>
+      <c r="C100" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D100" t="s">
         <v>50</v>
@@ -9450,7 +9543,7 @@
         <v>869</v>
       </c>
       <c r="Q100" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R100" t="s">
         <v>1046</v>
@@ -9472,8 +9565,9 @@
       <c r="B101" t="s">
         <v>870</v>
       </c>
-      <c r="C101" t="s">
-        <v>15</v>
+      <c r="C101" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D101" t="s">
         <v>50</v>
@@ -9512,7 +9606,7 @@
         <v>870</v>
       </c>
       <c r="Q101" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R101" t="s">
         <v>1047</v>
@@ -9534,8 +9628,9 @@
       <c r="B102" t="s">
         <v>871</v>
       </c>
-      <c r="C102" t="s">
-        <v>15</v>
+      <c r="C102" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D102" t="s">
         <v>50</v>
@@ -9574,7 +9669,7 @@
         <v>871</v>
       </c>
       <c r="Q102" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R102" t="s">
         <v>1048</v>
@@ -9596,8 +9691,9 @@
       <c r="B103" t="s">
         <v>872</v>
       </c>
-      <c r="C103" t="s">
-        <v>15</v>
+      <c r="C103" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D103" t="s">
         <v>50</v>
@@ -9636,7 +9732,7 @@
         <v>872</v>
       </c>
       <c r="Q103" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R103" t="s">
         <v>1049</v>
@@ -9658,8 +9754,9 @@
       <c r="B104" t="s">
         <v>873</v>
       </c>
-      <c r="C104" t="s">
-        <v>15</v>
+      <c r="C104" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D104" t="s">
         <v>50</v>
@@ -9698,7 +9795,7 @@
         <v>873</v>
       </c>
       <c r="Q104" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R104" t="s">
         <v>1050</v>
@@ -9720,8 +9817,9 @@
       <c r="B105" t="s">
         <v>874</v>
       </c>
-      <c r="C105" t="s">
-        <v>15</v>
+      <c r="C105" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D105" t="s">
         <v>50</v>
@@ -9760,7 +9858,7 @@
         <v>874</v>
       </c>
       <c r="Q105" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R105" t="s">
         <v>1051</v>
@@ -9782,8 +9880,9 @@
       <c r="B106" t="s">
         <v>875</v>
       </c>
-      <c r="C106" t="s">
-        <v>15</v>
+      <c r="C106" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D106" t="s">
         <v>50</v>
@@ -9822,7 +9921,7 @@
         <v>875</v>
       </c>
       <c r="Q106" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R106" t="s">
         <v>1052</v>
@@ -9844,8 +9943,9 @@
       <c r="B107" t="s">
         <v>876</v>
       </c>
-      <c r="C107" t="s">
-        <v>15</v>
+      <c r="C107" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D107" t="s">
         <v>50</v>
@@ -9884,7 +9984,7 @@
         <v>876</v>
       </c>
       <c r="Q107" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R107" t="s">
         <v>1053</v>
@@ -9906,8 +10006,9 @@
       <c r="B108" t="s">
         <v>877</v>
       </c>
-      <c r="C108" t="s">
-        <v>15</v>
+      <c r="C108" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D108" t="s">
         <v>50</v>
@@ -9946,7 +10047,7 @@
         <v>877</v>
       </c>
       <c r="Q108" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R108" t="s">
         <v>1054</v>
@@ -9968,8 +10069,9 @@
       <c r="B109" t="s">
         <v>878</v>
       </c>
-      <c r="C109" t="s">
-        <v>15</v>
+      <c r="C109" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D109" t="s">
         <v>50</v>
@@ -10008,7 +10110,7 @@
         <v>878</v>
       </c>
       <c r="Q109" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R109" t="s">
         <v>1055</v>
@@ -10030,8 +10132,9 @@
       <c r="B110" t="s">
         <v>879</v>
       </c>
-      <c r="C110" t="s">
-        <v>15</v>
+      <c r="C110" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D110" t="s">
         <v>50</v>
@@ -10070,7 +10173,7 @@
         <v>879</v>
       </c>
       <c r="Q110" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R110" t="s">
         <v>1056</v>
@@ -10092,8 +10195,9 @@
       <c r="B111" t="s">
         <v>880</v>
       </c>
-      <c r="C111" t="s">
-        <v>15</v>
+      <c r="C111" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D111" t="s">
         <v>50</v>
@@ -10132,7 +10236,7 @@
         <v>880</v>
       </c>
       <c r="Q111" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R111" t="s">
         <v>1057</v>
@@ -10154,8 +10258,9 @@
       <c r="B112" t="s">
         <v>881</v>
       </c>
-      <c r="C112" t="s">
-        <v>15</v>
+      <c r="C112" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D112" t="s">
         <v>50</v>
@@ -10194,7 +10299,7 @@
         <v>881</v>
       </c>
       <c r="Q112" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R112" t="s">
         <v>1058</v>
@@ -10216,8 +10321,9 @@
       <c r="B113" t="s">
         <v>882</v>
       </c>
-      <c r="C113" t="s">
-        <v>15</v>
+      <c r="C113" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D113" t="s">
         <v>50</v>
@@ -10256,7 +10362,7 @@
         <v>882</v>
       </c>
       <c r="Q113" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R113" t="s">
         <v>1059</v>
@@ -10278,8 +10384,9 @@
       <c r="B114" t="s">
         <v>883</v>
       </c>
-      <c r="C114" t="s">
-        <v>15</v>
+      <c r="C114" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D114" t="s">
         <v>50</v>
@@ -10318,7 +10425,7 @@
         <v>883</v>
       </c>
       <c r="Q114" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R114" t="s">
         <v>1060</v>
@@ -10340,8 +10447,9 @@
       <c r="B115" t="s">
         <v>884</v>
       </c>
-      <c r="C115" t="s">
-        <v>15</v>
+      <c r="C115" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D115" t="s">
         <v>50</v>
@@ -10380,7 +10488,7 @@
         <v>884</v>
       </c>
       <c r="Q115" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R115" t="s">
         <v>1061</v>
@@ -10402,8 +10510,9 @@
       <c r="B116" t="s">
         <v>885</v>
       </c>
-      <c r="C116" t="s">
-        <v>15</v>
+      <c r="C116" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D116" t="s">
         <v>50</v>
@@ -10442,7 +10551,7 @@
         <v>885</v>
       </c>
       <c r="Q116" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R116" t="s">
         <v>1062</v>
@@ -10464,8 +10573,9 @@
       <c r="B117" t="s">
         <v>886</v>
       </c>
-      <c r="C117" t="s">
-        <v>15</v>
+      <c r="C117" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D117" t="s">
         <v>50</v>
@@ -10504,7 +10614,7 @@
         <v>886</v>
       </c>
       <c r="Q117" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R117" t="s">
         <v>1063</v>
@@ -10526,8 +10636,9 @@
       <c r="B118" t="s">
         <v>887</v>
       </c>
-      <c r="C118" t="s">
-        <v>15</v>
+      <c r="C118" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D118" t="s">
         <v>50</v>
@@ -10566,7 +10677,7 @@
         <v>887</v>
       </c>
       <c r="Q118" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R118" t="s">
         <v>1064</v>
@@ -10588,8 +10699,9 @@
       <c r="B119" t="s">
         <v>888</v>
       </c>
-      <c r="C119" t="s">
-        <v>15</v>
+      <c r="C119" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D119" t="s">
         <v>50</v>
@@ -10628,7 +10740,7 @@
         <v>888</v>
       </c>
       <c r="Q119" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R119" t="s">
         <v>1065</v>
@@ -10650,8 +10762,9 @@
       <c r="B120" t="s">
         <v>889</v>
       </c>
-      <c r="C120" t="s">
-        <v>15</v>
+      <c r="C120" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D120" t="s">
         <v>50</v>
@@ -10690,7 +10803,7 @@
         <v>889</v>
       </c>
       <c r="Q120" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R120" t="s">
         <v>1066</v>
@@ -10712,8 +10825,9 @@
       <c r="B121" t="s">
         <v>890</v>
       </c>
-      <c r="C121" t="s">
-        <v>15</v>
+      <c r="C121" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D121" t="s">
         <v>50</v>
@@ -10752,7 +10866,7 @@
         <v>890</v>
       </c>
       <c r="Q121" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R121" t="s">
         <v>1067</v>
@@ -10774,8 +10888,9 @@
       <c r="B122" t="s">
         <v>891</v>
       </c>
-      <c r="C122" t="s">
-        <v>15</v>
+      <c r="C122" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D122" t="s">
         <v>50</v>
@@ -10814,7 +10929,7 @@
         <v>891</v>
       </c>
       <c r="Q122" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R122" t="s">
         <v>1068</v>
@@ -10836,8 +10951,9 @@
       <c r="B123" t="s">
         <v>892</v>
       </c>
-      <c r="C123" t="s">
-        <v>15</v>
+      <c r="C123" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D123" t="s">
         <v>50</v>
@@ -10876,7 +10992,7 @@
         <v>892</v>
       </c>
       <c r="Q123" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R123" t="s">
         <v>1069</v>
@@ -10898,8 +11014,9 @@
       <c r="B124" t="s">
         <v>893</v>
       </c>
-      <c r="C124" t="s">
-        <v>15</v>
+      <c r="C124" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D124" t="s">
         <v>50</v>
@@ -10938,7 +11055,7 @@
         <v>893</v>
       </c>
       <c r="Q124" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R124" t="s">
         <v>1070</v>
@@ -10960,8 +11077,9 @@
       <c r="B125" t="s">
         <v>894</v>
       </c>
-      <c r="C125" t="s">
-        <v>15</v>
+      <c r="C125" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D125" t="s">
         <v>50</v>
@@ -11000,7 +11118,7 @@
         <v>894</v>
       </c>
       <c r="Q125" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R125" t="s">
         <v>1071</v>
@@ -11022,8 +11140,9 @@
       <c r="B126" t="s">
         <v>895</v>
       </c>
-      <c r="C126" t="s">
-        <v>15</v>
+      <c r="C126" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D126" t="s">
         <v>50</v>
@@ -11062,7 +11181,7 @@
         <v>895</v>
       </c>
       <c r="Q126" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R126" t="s">
         <v>1072</v>
@@ -11084,8 +11203,9 @@
       <c r="B127" t="s">
         <v>896</v>
       </c>
-      <c r="C127" t="s">
-        <v>15</v>
+      <c r="C127" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D127" t="s">
         <v>50</v>
@@ -11124,7 +11244,7 @@
         <v>896</v>
       </c>
       <c r="Q127" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R127" t="s">
         <v>1073</v>
@@ -11146,8 +11266,9 @@
       <c r="B128" t="s">
         <v>897</v>
       </c>
-      <c r="C128" t="s">
-        <v>15</v>
+      <c r="C128" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D128" t="s">
         <v>50</v>
@@ -11186,7 +11307,7 @@
         <v>897</v>
       </c>
       <c r="Q128" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R128" t="s">
         <v>1074</v>
@@ -11208,8 +11329,9 @@
       <c r="B129" t="s">
         <v>898</v>
       </c>
-      <c r="C129" t="s">
-        <v>15</v>
+      <c r="C129" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D129" t="s">
         <v>50</v>
@@ -11248,7 +11370,7 @@
         <v>898</v>
       </c>
       <c r="Q129" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R129" t="s">
         <v>1075</v>
@@ -11270,8 +11392,9 @@
       <c r="B130" t="s">
         <v>899</v>
       </c>
-      <c r="C130" t="s">
-        <v>15</v>
+      <c r="C130" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D130" t="s">
         <v>50</v>
@@ -11310,7 +11433,7 @@
         <v>899</v>
       </c>
       <c r="Q130" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R130" t="s">
         <v>1076</v>
@@ -11332,8 +11455,9 @@
       <c r="B131" t="s">
         <v>900</v>
       </c>
-      <c r="C131" t="s">
-        <v>15</v>
+      <c r="C131" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D131" t="s">
         <v>50</v>
@@ -11372,7 +11496,7 @@
         <v>900</v>
       </c>
       <c r="Q131" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R131" t="s">
         <v>1077</v>
@@ -11394,8 +11518,9 @@
       <c r="B132" t="s">
         <v>901</v>
       </c>
-      <c r="C132" t="s">
-        <v>15</v>
+      <c r="C132" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D132" t="s">
         <v>50</v>
@@ -11434,7 +11559,7 @@
         <v>901</v>
       </c>
       <c r="Q132" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R132" t="s">
         <v>1078</v>
@@ -11456,8 +11581,9 @@
       <c r="B133" t="s">
         <v>902</v>
       </c>
-      <c r="C133" t="s">
-        <v>15</v>
+      <c r="C133" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D133" t="s">
         <v>50</v>
@@ -11496,7 +11622,7 @@
         <v>902</v>
       </c>
       <c r="Q133" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R133" t="s">
         <v>1079</v>
@@ -11518,8 +11644,9 @@
       <c r="B134" t="s">
         <v>903</v>
       </c>
-      <c r="C134" t="s">
-        <v>15</v>
+      <c r="C134" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D134" t="s">
         <v>50</v>
@@ -11558,7 +11685,7 @@
         <v>903</v>
       </c>
       <c r="Q134" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R134" t="s">
         <v>1080</v>
@@ -11580,8 +11707,9 @@
       <c r="B135" t="s">
         <v>904</v>
       </c>
-      <c r="C135" t="s">
-        <v>15</v>
+      <c r="C135" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D135" t="s">
         <v>50</v>
@@ -11620,7 +11748,7 @@
         <v>904</v>
       </c>
       <c r="Q135" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R135" t="s">
         <v>1081</v>
@@ -11642,8 +11770,9 @@
       <c r="B136" t="s">
         <v>905</v>
       </c>
-      <c r="C136" t="s">
-        <v>15</v>
+      <c r="C136" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D136" t="s">
         <v>50</v>
@@ -11682,7 +11811,7 @@
         <v>905</v>
       </c>
       <c r="Q136" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R136" t="s">
         <v>1082</v>
@@ -11704,8 +11833,9 @@
       <c r="B137" t="s">
         <v>906</v>
       </c>
-      <c r="C137" t="s">
-        <v>15</v>
+      <c r="C137" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D137" t="s">
         <v>50</v>
@@ -11744,7 +11874,7 @@
         <v>906</v>
       </c>
       <c r="Q137" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R137" t="s">
         <v>1083</v>
@@ -11766,8 +11896,9 @@
       <c r="B138" t="s">
         <v>907</v>
       </c>
-      <c r="C138" t="s">
-        <v>15</v>
+      <c r="C138" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D138" t="s">
         <v>50</v>
@@ -11806,7 +11937,7 @@
         <v>907</v>
       </c>
       <c r="Q138" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R138" t="s">
         <v>1084</v>
@@ -11828,8 +11959,9 @@
       <c r="B139" t="s">
         <v>908</v>
       </c>
-      <c r="C139" t="s">
-        <v>15</v>
+      <c r="C139" t="str">
+        <f t="shared" si="1"/>
+        <v>\I: POL</v>
       </c>
       <c r="D139" t="s">
         <v>50</v>
@@ -11868,7 +12000,7 @@
         <v>908</v>
       </c>
       <c r="Q139" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R139" t="s">
         <v>1085</v>
@@ -11890,8 +12022,9 @@
       <c r="B140" t="s">
         <v>909</v>
       </c>
-      <c r="C140" t="s">
-        <v>15</v>
+      <c r="C140" t="str">
+        <f t="shared" ref="C140:C187" si="2">Q140</f>
+        <v>\I: POL</v>
       </c>
       <c r="D140" t="s">
         <v>50</v>
@@ -11930,7 +12063,7 @@
         <v>909</v>
       </c>
       <c r="Q140" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R140" t="s">
         <v>1086</v>
@@ -11952,8 +12085,9 @@
       <c r="B141" t="s">
         <v>910</v>
       </c>
-      <c r="C141" t="s">
-        <v>15</v>
+      <c r="C141" t="str">
+        <f t="shared" si="2"/>
+        <v>\I: POL</v>
       </c>
       <c r="D141" t="s">
         <v>50</v>
@@ -11992,7 +12126,7 @@
         <v>910</v>
       </c>
       <c r="Q141" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R141" t="s">
         <v>1087</v>
@@ -12014,8 +12148,9 @@
       <c r="B142" t="s">
         <v>911</v>
       </c>
-      <c r="C142" t="s">
-        <v>15</v>
+      <c r="C142" t="str">
+        <f t="shared" si="2"/>
+        <v>\I: POL</v>
       </c>
       <c r="D142" t="s">
         <v>50</v>
@@ -12054,7 +12189,7 @@
         <v>911</v>
       </c>
       <c r="Q142" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R142" t="s">
         <v>1088</v>
@@ -12076,8 +12211,9 @@
       <c r="B143" t="s">
         <v>912</v>
       </c>
-      <c r="C143" t="s">
-        <v>15</v>
+      <c r="C143" t="str">
+        <f t="shared" si="2"/>
+        <v>\I: POL</v>
       </c>
       <c r="D143" t="s">
         <v>50</v>
@@ -12116,7 +12252,7 @@
         <v>912</v>
       </c>
       <c r="Q143" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R143" t="s">
         <v>1089</v>
@@ -12138,8 +12274,9 @@
       <c r="B144" t="s">
         <v>913</v>
       </c>
-      <c r="C144" t="s">
-        <v>15</v>
+      <c r="C144" t="str">
+        <f t="shared" si="2"/>
+        <v>\I: POL</v>
       </c>
       <c r="D144" t="s">
         <v>50</v>
@@ -12178,7 +12315,7 @@
         <v>913</v>
       </c>
       <c r="Q144" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R144" t="s">
         <v>1090</v>
@@ -12200,8 +12337,9 @@
       <c r="B145" t="s">
         <v>914</v>
       </c>
-      <c r="C145" t="s">
-        <v>15</v>
+      <c r="C145" t="str">
+        <f t="shared" si="2"/>
+        <v>\I: POL</v>
       </c>
       <c r="D145" t="s">
         <v>50</v>
@@ -12240,7 +12378,7 @@
         <v>914</v>
       </c>
       <c r="Q145" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R145" t="s">
         <v>1091</v>
@@ -12262,8 +12400,9 @@
       <c r="B146" t="s">
         <v>915</v>
       </c>
-      <c r="C146" t="s">
-        <v>15</v>
+      <c r="C146" t="str">
+        <f t="shared" si="2"/>
+        <v>\I: POL</v>
       </c>
       <c r="D146" t="s">
         <v>50</v>
@@ -12302,7 +12441,7 @@
         <v>915</v>
       </c>
       <c r="Q146" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R146" t="s">
         <v>1092</v>
@@ -12324,8 +12463,9 @@
       <c r="B147" t="s">
         <v>916</v>
       </c>
-      <c r="C147" t="s">
-        <v>15</v>
+      <c r="C147" t="str">
+        <f t="shared" si="2"/>
+        <v>\I: POL</v>
       </c>
       <c r="D147" t="s">
         <v>50</v>
@@ -12364,7 +12504,7 @@
         <v>916</v>
       </c>
       <c r="Q147" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R147" t="s">
         <v>1093</v>
@@ -12386,8 +12526,9 @@
       <c r="B148" t="s">
         <v>917</v>
       </c>
-      <c r="C148" t="s">
-        <v>15</v>
+      <c r="C148" t="str">
+        <f t="shared" si="2"/>
+        <v>\I: POL</v>
       </c>
       <c r="D148" t="s">
         <v>50</v>
@@ -12426,7 +12567,7 @@
         <v>917</v>
       </c>
       <c r="Q148" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R148" t="s">
         <v>1094</v>
@@ -12448,8 +12589,9 @@
       <c r="B149" t="s">
         <v>918</v>
       </c>
-      <c r="C149" t="s">
-        <v>15</v>
+      <c r="C149" t="str">
+        <f t="shared" si="2"/>
+        <v>\I: POL</v>
       </c>
       <c r="D149" t="s">
         <v>50</v>
@@ -12488,7 +12630,7 @@
         <v>918</v>
       </c>
       <c r="Q149" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R149" t="s">
         <v>1095</v>
@@ -12510,8 +12652,9 @@
       <c r="B150" t="s">
         <v>919</v>
       </c>
-      <c r="C150" t="s">
-        <v>15</v>
+      <c r="C150" t="str">
+        <f t="shared" si="2"/>
+        <v>\I: POL</v>
       </c>
       <c r="D150" t="s">
         <v>50</v>
@@ -12550,7 +12693,7 @@
         <v>919</v>
       </c>
       <c r="Q150" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R150" t="s">
         <v>1096</v>
@@ -12572,8 +12715,9 @@
       <c r="B151" t="s">
         <v>920</v>
       </c>
-      <c r="C151" t="s">
-        <v>15</v>
+      <c r="C151" t="str">
+        <f t="shared" si="2"/>
+        <v>\I: POL</v>
       </c>
       <c r="D151" t="s">
         <v>50</v>
@@ -12612,7 +12756,7 @@
         <v>920</v>
       </c>
       <c r="Q151" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R151" t="s">
         <v>1097</v>
@@ -12634,8 +12778,9 @@
       <c r="B152" t="s">
         <v>921</v>
       </c>
-      <c r="C152" t="s">
-        <v>15</v>
+      <c r="C152" t="str">
+        <f t="shared" si="2"/>
+        <v>\I: POL</v>
       </c>
       <c r="D152" t="s">
         <v>50</v>
@@ -12674,7 +12819,7 @@
         <v>921</v>
       </c>
       <c r="Q152" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R152" t="s">
         <v>1098</v>
@@ -12696,8 +12841,9 @@
       <c r="B153" t="s">
         <v>922</v>
       </c>
-      <c r="C153" t="s">
-        <v>15</v>
+      <c r="C153" t="str">
+        <f t="shared" si="2"/>
+        <v>\I: POL</v>
       </c>
       <c r="D153" t="s">
         <v>50</v>
@@ -12736,7 +12882,7 @@
         <v>922</v>
       </c>
       <c r="Q153" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R153" t="s">
         <v>1099</v>
@@ -12758,8 +12904,9 @@
       <c r="B154" t="s">
         <v>923</v>
       </c>
-      <c r="C154" t="s">
-        <v>15</v>
+      <c r="C154" t="str">
+        <f t="shared" si="2"/>
+        <v>\I: POL</v>
       </c>
       <c r="D154" t="s">
         <v>50</v>
@@ -12798,7 +12945,7 @@
         <v>923</v>
       </c>
       <c r="Q154" t="s">
-        <v>15</v>
+        <v>1134</v>
       </c>
       <c r="R154" t="s">
         <v>1100</v>
@@ -12820,8 +12967,9 @@
       <c r="B155" t="s">
         <v>924</v>
       </c>
-      <c r="C155" t="s">
-        <v>15</v>
+      <c r="C155" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D155" t="s">
         <v>202</v>
@@ -12882,8 +13030,9 @@
       <c r="B156" t="s">
         <v>925</v>
       </c>
-      <c r="C156" t="s">
-        <v>15</v>
+      <c r="C156" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D156" t="s">
         <v>202</v>
@@ -12944,8 +13093,9 @@
       <c r="B157" t="s">
         <v>926</v>
       </c>
-      <c r="C157" t="s">
-        <v>15</v>
+      <c r="C157" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D157" t="s">
         <v>202</v>
@@ -13006,8 +13156,9 @@
       <c r="B158" t="s">
         <v>927</v>
       </c>
-      <c r="C158" t="s">
-        <v>15</v>
+      <c r="C158" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D158" t="s">
         <v>202</v>
@@ -13068,8 +13219,9 @@
       <c r="B159" t="s">
         <v>928</v>
       </c>
-      <c r="C159" t="s">
-        <v>15</v>
+      <c r="C159" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D159" t="s">
         <v>202</v>
@@ -13130,8 +13282,9 @@
       <c r="B160" t="s">
         <v>929</v>
       </c>
-      <c r="C160" t="s">
-        <v>15</v>
+      <c r="C160" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D160" t="s">
         <v>202</v>
@@ -13192,8 +13345,9 @@
       <c r="B161" t="s">
         <v>930</v>
       </c>
-      <c r="C161" t="s">
-        <v>15</v>
+      <c r="C161" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D161" t="s">
         <v>202</v>
@@ -13254,8 +13408,9 @@
       <c r="B162" t="s">
         <v>931</v>
       </c>
-      <c r="C162" t="s">
-        <v>15</v>
+      <c r="C162" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D162" t="s">
         <v>202</v>
@@ -13316,8 +13471,9 @@
       <c r="B163" t="s">
         <v>932</v>
       </c>
-      <c r="C163" t="s">
-        <v>15</v>
+      <c r="C163" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D163" t="s">
         <v>202</v>
@@ -13378,8 +13534,9 @@
       <c r="B164" t="s">
         <v>933</v>
       </c>
-      <c r="C164" t="s">
-        <v>15</v>
+      <c r="C164" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D164" t="s">
         <v>202</v>
@@ -13440,8 +13597,9 @@
       <c r="B165" t="s">
         <v>934</v>
       </c>
-      <c r="C165" t="s">
-        <v>15</v>
+      <c r="C165" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D165" t="s">
         <v>202</v>
@@ -13502,8 +13660,9 @@
       <c r="B166" t="s">
         <v>935</v>
       </c>
-      <c r="C166" t="s">
-        <v>15</v>
+      <c r="C166" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D166" t="s">
         <v>202</v>
@@ -13564,8 +13723,9 @@
       <c r="B167" t="s">
         <v>936</v>
       </c>
-      <c r="C167" t="s">
-        <v>15</v>
+      <c r="C167" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D167" t="s">
         <v>202</v>
@@ -13626,8 +13786,9 @@
       <c r="B168" t="s">
         <v>937</v>
       </c>
-      <c r="C168" t="s">
-        <v>15</v>
+      <c r="C168" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D168" t="s">
         <v>202</v>
@@ -13688,8 +13849,9 @@
       <c r="B169" t="s">
         <v>938</v>
       </c>
-      <c r="C169" t="s">
-        <v>15</v>
+      <c r="C169" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D169" t="s">
         <v>202</v>
@@ -13750,8 +13912,9 @@
       <c r="B170" t="s">
         <v>939</v>
       </c>
-      <c r="C170" t="s">
-        <v>15</v>
+      <c r="C170" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D170" t="s">
         <v>202</v>
@@ -13812,8 +13975,9 @@
       <c r="B171" t="s">
         <v>940</v>
       </c>
-      <c r="C171" t="s">
-        <v>15</v>
+      <c r="C171" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D171" t="s">
         <v>202</v>
@@ -13874,8 +14038,9 @@
       <c r="B172" t="s">
         <v>941</v>
       </c>
-      <c r="C172" t="s">
-        <v>15</v>
+      <c r="C172" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D172" t="s">
         <v>202</v>
@@ -13936,8 +14101,9 @@
       <c r="B173" t="s">
         <v>942</v>
       </c>
-      <c r="C173" t="s">
-        <v>15</v>
+      <c r="C173" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D173" t="s">
         <v>202</v>
@@ -13998,8 +14164,9 @@
       <c r="B174" t="s">
         <v>943</v>
       </c>
-      <c r="C174" t="s">
-        <v>15</v>
+      <c r="C174" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D174" t="s">
         <v>202</v>
@@ -14060,8 +14227,9 @@
       <c r="B175" t="s">
         <v>944</v>
       </c>
-      <c r="C175" t="s">
-        <v>15</v>
+      <c r="C175" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D175" t="s">
         <v>202</v>
@@ -14122,8 +14290,9 @@
       <c r="B176" t="s">
         <v>945</v>
       </c>
-      <c r="C176" t="s">
-        <v>15</v>
+      <c r="C176" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D176" t="s">
         <v>202</v>
@@ -14184,8 +14353,9 @@
       <c r="B177" t="s">
         <v>946</v>
       </c>
-      <c r="C177" t="s">
-        <v>15</v>
+      <c r="C177" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D177" t="s">
         <v>202</v>
@@ -14246,8 +14416,9 @@
       <c r="B178" t="s">
         <v>947</v>
       </c>
-      <c r="C178" t="s">
-        <v>15</v>
+      <c r="C178" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D178" t="s">
         <v>202</v>
@@ -14308,8 +14479,9 @@
       <c r="B179" t="s">
         <v>948</v>
       </c>
-      <c r="C179" t="s">
-        <v>15</v>
+      <c r="C179" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D179" t="s">
         <v>202</v>
@@ -14370,8 +14542,9 @@
       <c r="B180" t="s">
         <v>949</v>
       </c>
-      <c r="C180" t="s">
-        <v>15</v>
+      <c r="C180" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D180" t="s">
         <v>202</v>
@@ -14432,8 +14605,9 @@
       <c r="B181" t="s">
         <v>950</v>
       </c>
-      <c r="C181" t="s">
-        <v>15</v>
+      <c r="C181" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D181" t="s">
         <v>202</v>
@@ -14494,8 +14668,9 @@
       <c r="B182" t="s">
         <v>951</v>
       </c>
-      <c r="C182" t="s">
-        <v>15</v>
+      <c r="C182" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D182" t="s">
         <v>202</v>
@@ -14556,8 +14731,9 @@
       <c r="B183" t="s">
         <v>952</v>
       </c>
-      <c r="C183" t="s">
-        <v>15</v>
+      <c r="C183" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D183" t="s">
         <v>202</v>
@@ -14618,8 +14794,9 @@
       <c r="B184" t="s">
         <v>953</v>
       </c>
-      <c r="C184" t="s">
-        <v>15</v>
+      <c r="C184" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D184" t="s">
         <v>202</v>
@@ -14680,8 +14857,9 @@
       <c r="B185" t="s">
         <v>954</v>
       </c>
-      <c r="C185" t="s">
-        <v>15</v>
+      <c r="C185" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D185" t="s">
         <v>202</v>
@@ -14742,8 +14920,9 @@
       <c r="B186" t="s">
         <v>955</v>
       </c>
-      <c r="C186" t="s">
-        <v>15</v>
+      <c r="C186" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D186" t="s">
         <v>202</v>
@@ -14804,8 +14983,9 @@
       <c r="B187" t="s">
         <v>956</v>
       </c>
-      <c r="C187" t="s">
-        <v>15</v>
+      <c r="C187" t="str">
+        <f t="shared" si="2"/>
+        <v>POL</v>
       </c>
       <c r="D187" t="s">
         <v>202</v>
